--- a/data/A111223022/ranking_records.xlsx
+++ b/data/A111223022/ranking_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>學年</t>
   </si>
@@ -465,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="6" width="16.7109375" style="1" customWidth="1"/>
@@ -552,28 +552,28 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
       <c r="D3">
-        <v>91.3</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>38</v>
@@ -587,22 +587,22 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>91.3</v>
+        <v>91.8</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -614,33 +614,33 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L4">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -652,42 +652,42 @@
         <v>2</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>93</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="J6">
         <v>38</v>
@@ -696,36 +696,36 @@
         <v>38</v>
       </c>
       <c r="L6">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>93</v>
+        <v>81.5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="J7">
         <v>38</v>
@@ -734,462 +734,6 @@
         <v>38</v>
       </c>
       <c r="L7">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>91.8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>40</v>
-      </c>
-      <c r="K8">
-        <v>40</v>
-      </c>
-      <c r="L8">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9">
-        <v>91.8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>40</v>
-      </c>
-      <c r="L9">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>91.8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10">
-        <v>9</v>
-      </c>
-      <c r="J10">
-        <v>40</v>
-      </c>
-      <c r="K10">
-        <v>40</v>
-      </c>
-      <c r="L10">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>97</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>39</v>
-      </c>
-      <c r="K11">
-        <v>39</v>
-      </c>
-      <c r="L11">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12">
-        <v>97</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12">
-        <v>39</v>
-      </c>
-      <c r="K12">
-        <v>39</v>
-      </c>
-      <c r="L12">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13">
-        <v>97</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>39</v>
-      </c>
-      <c r="K13">
-        <v>39</v>
-      </c>
-      <c r="L13">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14">
-        <v>9</v>
-      </c>
-      <c r="H14">
-        <v>9</v>
-      </c>
-      <c r="I14">
-        <v>62</v>
-      </c>
-      <c r="J14">
-        <v>38</v>
-      </c>
-      <c r="K14">
-        <v>38</v>
-      </c>
-      <c r="L14">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15">
-        <v>9</v>
-      </c>
-      <c r="H15">
-        <v>9</v>
-      </c>
-      <c r="I15">
-        <v>62</v>
-      </c>
-      <c r="J15">
-        <v>38</v>
-      </c>
-      <c r="K15">
-        <v>38</v>
-      </c>
-      <c r="L15">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16">
-        <v>9</v>
-      </c>
-      <c r="H16">
-        <v>9</v>
-      </c>
-      <c r="I16">
-        <v>62</v>
-      </c>
-      <c r="J16">
-        <v>38</v>
-      </c>
-      <c r="K16">
-        <v>38</v>
-      </c>
-      <c r="L16">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17">
-        <v>81.5</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17">
-        <v>14</v>
-      </c>
-      <c r="H17">
-        <v>14</v>
-      </c>
-      <c r="I17">
-        <v>91</v>
-      </c>
-      <c r="J17">
-        <v>38</v>
-      </c>
-      <c r="K17">
-        <v>38</v>
-      </c>
-      <c r="L17">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18">
-        <v>81.5</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18">
-        <v>14</v>
-      </c>
-      <c r="H18">
-        <v>14</v>
-      </c>
-      <c r="I18">
-        <v>91</v>
-      </c>
-      <c r="J18">
-        <v>38</v>
-      </c>
-      <c r="K18">
-        <v>38</v>
-      </c>
-      <c r="L18">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19">
-        <v>81.5</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19">
-        <v>14</v>
-      </c>
-      <c r="H19">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>91</v>
-      </c>
-      <c r="J19">
-        <v>38</v>
-      </c>
-      <c r="K19">
-        <v>38</v>
-      </c>
-      <c r="L19">
         <v>160</v>
       </c>
     </row>
